--- a/Mẫu thông tin nhân viên.xlsx
+++ b/Mẫu thông tin nhân viên.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vietstargroup\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nghia\Desktop\temp\blockchainHC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27121ED-C675-4998-828B-1255FEC1A40E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E82ED23-6809-45C1-B2AA-62008BDB986D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11775" xr2:uid="{0B8F0A66-3EF3-4759-B4C1-B9F12DEC6208}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0B8F0A66-3EF3-4759-B4C1-B9F12DEC6208}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1341,12 +1338,190 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1367,9 +1542,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1386,188 +1558,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="20" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1587,37 +1577,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="DS_Nhân viên Vietstar"/>
-      <sheetName val="DS_Nhân viên Smartbank"/>
-      <sheetName val="DS VS_Nhân viên nghỉ việc"/>
-      <sheetName val="DS HCM_Nhân viên nghỉ việc"/>
-      <sheetName val="HĐLĐ VS"/>
-      <sheetName val="HĐLĐ HCM"/>
-      <sheetName val="HĐLĐ Smartbank"/>
-      <sheetName val="HDDV"/>
-      <sheetName val="QĐNV"/>
-      <sheetName val="System_Added_DoNotRemove"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1917,448 +1876,452 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142115CF-756B-4A06-B7F1-4E8136E88307}">
-  <dimension ref="A1:EW3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="28" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="76" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="46" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="11" style="46" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="76" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="46" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="46" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" style="46" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="46" customWidth="1"/>
-    <col min="12" max="12" width="18" style="46" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="76" customWidth="1"/>
-    <col min="14" max="14" width="56" style="46" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="82.42578125" style="28" customWidth="1"/>
-    <col min="16" max="16" width="90.5703125" style="77" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.7109375" style="28" customWidth="1"/>
-    <col min="18" max="18" width="41.42578125" style="28" customWidth="1"/>
-    <col min="19" max="19" width="16" style="46" customWidth="1"/>
-    <col min="20" max="20" width="27.140625" style="46" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="34.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.28515625" style="46" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.5703125" style="46" customWidth="1"/>
-    <col min="24" max="24" width="24.5703125" style="46" customWidth="1"/>
-    <col min="25" max="25" width="12" style="28" customWidth="1"/>
-    <col min="26" max="26" width="16.85546875" style="28" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="28" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="28" customWidth="1"/>
-    <col min="29" max="29" width="25" style="28" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5703125" style="28" customWidth="1"/>
-    <col min="31" max="31" width="19.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12" style="28" customWidth="1"/>
-    <col min="34" max="34" width="31.28515625" style="28" customWidth="1"/>
-    <col min="35" max="35" width="26.5703125" style="74" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="20.85546875" style="74" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="18.28515625" style="74" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="10.140625" style="75" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="9.140625" style="26" customWidth="1"/>
-    <col min="40" max="52" width="14.42578125" style="26"/>
-    <col min="53" max="153" width="14.42578125" style="27"/>
-    <col min="154" max="16384" width="14.42578125" style="28"/>
+    <col min="1" max="1" width="4.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="51" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="23" customWidth="1"/>
+    <col min="6" max="6" width="11" style="23" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="51" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="23" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="23" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="23" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="18" style="23" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="51" customWidth="1"/>
+    <col min="14" max="14" width="56" style="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="82.42578125" style="6" customWidth="1"/>
+    <col min="16" max="16" width="90.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="31.7109375" style="6" customWidth="1"/>
+    <col min="18" max="18" width="41.42578125" style="6" customWidth="1"/>
+    <col min="19" max="19" width="16" style="23" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="34.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.5703125" style="23" customWidth="1"/>
+    <col min="24" max="24" width="24.5703125" style="23" customWidth="1"/>
+    <col min="25" max="25" width="12" style="6" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" style="6" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="6" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="6" customWidth="1"/>
+    <col min="29" max="29" width="25" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" style="6" customWidth="1"/>
+    <col min="31" max="31" width="19.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" style="6" customWidth="1"/>
+    <col min="34" max="34" width="31.28515625" style="6" customWidth="1"/>
+    <col min="35" max="35" width="26.5703125" style="50" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="20.85546875" style="50" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="18.28515625" style="50" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="10.140625" style="50" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="9.140625" style="5" customWidth="1"/>
+    <col min="40" max="52" width="14.42578125" style="5"/>
+    <col min="53" max="16384" width="14.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:151" ht="66" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:42" ht="66" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="64"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="9" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="10"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="12" t="s">
+      <c r="M1" s="69"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="14" t="s">
+      <c r="P1" s="72"/>
+      <c r="Q1" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="9" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="17" t="s">
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="19" t="s">
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="20" t="s">
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="AC1" s="21"/>
-      <c r="AD1" s="22" t="s">
+      <c r="AC1" s="59"/>
+      <c r="AD1" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="AE1" s="21"/>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="21"/>
-      <c r="AH1" s="23" t="s">
+      <c r="AE1" s="59"/>
+      <c r="AF1" s="59"/>
+      <c r="AG1" s="59"/>
+      <c r="AH1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AI1" s="23" t="s">
+      <c r="AI1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AJ1" s="23" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AK1" s="23" t="s">
+      <c r="AK1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AL1" s="24" t="s">
+      <c r="AL1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AM1" s="25"/>
+      <c r="AM1" s="4"/>
     </row>
-    <row r="2" spans="1:151" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="30" t="s">
+    <row r="2" spans="1:42" ht="82.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="62"/>
+      <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="40" t="s">
+      <c r="P2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="Q2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="30" t="s">
+      <c r="R2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="S2" s="41" t="s">
+      <c r="S2" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="30" t="s">
+      <c r="T2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="37" t="s">
+      <c r="U2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="42" t="s">
+      <c r="X2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="42" t="s">
+      <c r="Y2" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="Z2" s="43" t="s">
+      <c r="Z2" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="AA2" s="43" t="s">
+      <c r="AA2" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="AB2" s="44" t="s">
+      <c r="AB2" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="AC2" s="44" t="s">
+      <c r="AC2" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AD2" s="45" t="s">
+      <c r="AD2" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="AE2" s="45" t="s">
+      <c r="AE2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="AF2" s="45" t="s">
+      <c r="AF2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="AG2" s="45" t="s">
+      <c r="AG2" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="25"/>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="25"/>
-      <c r="AP2" s="25"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="4"/>
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+      <c r="AP2" s="4"/>
     </row>
-    <row r="3" spans="1:151" s="63" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+    <row r="3" spans="1:42" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="58" t="s">
+      <c r="L3" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="48" t="s">
+      <c r="N3" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="60" t="s">
+      <c r="O3" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="P3" s="60" t="s">
+      <c r="P3" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="Q3" s="49" t="s">
+      <c r="Q3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="R3" s="49" t="s">
+      <c r="R3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="65" t="s">
+      <c r="U3" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="50" t="s">
+      <c r="V3" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="W3" s="47" t="s">
+      <c r="W3" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="66" t="s">
+      <c r="X3" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="70"/>
-      <c r="AE3" s="70"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="71"/>
-      <c r="AH3" s="61"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="73"/>
-      <c r="AK3" s="62"/>
-      <c r="AL3" s="62"/>
-      <c r="AM3" s="62"/>
-      <c r="AN3" s="62"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="26"/>
-      <c r="AU3" s="26"/>
-      <c r="AV3" s="26"/>
-      <c r="AW3" s="26"/>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="26"/>
-      <c r="BR3" s="26"/>
-      <c r="BS3" s="26"/>
-      <c r="BT3" s="26"/>
-      <c r="BU3" s="26"/>
-      <c r="BV3" s="26"/>
-      <c r="BW3" s="26"/>
-      <c r="BX3" s="26"/>
-      <c r="BY3" s="26"/>
-      <c r="BZ3" s="26"/>
-      <c r="CA3" s="26"/>
-      <c r="CB3" s="26"/>
-      <c r="CC3" s="26"/>
-      <c r="CD3" s="26"/>
-      <c r="CE3" s="26"/>
-      <c r="CF3" s="26"/>
-      <c r="CG3" s="26"/>
-      <c r="CH3" s="26"/>
-      <c r="CI3" s="26"/>
-      <c r="CJ3" s="26"/>
-      <c r="CK3" s="26"/>
-      <c r="CL3" s="26"/>
-      <c r="CM3" s="26"/>
-      <c r="CN3" s="26"/>
-      <c r="CO3" s="26"/>
-      <c r="CP3" s="26"/>
-      <c r="CQ3" s="26"/>
-      <c r="CR3" s="26"/>
-      <c r="CS3" s="26"/>
-      <c r="CT3" s="26"/>
-      <c r="CU3" s="26"/>
-      <c r="CV3" s="26"/>
-      <c r="CW3" s="26"/>
-      <c r="CX3" s="26"/>
-      <c r="CY3" s="26"/>
-      <c r="CZ3" s="26"/>
-      <c r="DA3" s="26"/>
-      <c r="DB3" s="26"/>
-      <c r="DC3" s="26"/>
-      <c r="DD3" s="26"/>
-      <c r="DE3" s="26"/>
-      <c r="DF3" s="26"/>
-      <c r="DG3" s="26"/>
-      <c r="DH3" s="26"/>
-      <c r="DI3" s="26"/>
-      <c r="DJ3" s="26"/>
-      <c r="DK3" s="26"/>
-      <c r="DL3" s="26"/>
-      <c r="DM3" s="26"/>
-      <c r="DN3" s="26"/>
-      <c r="DO3" s="26"/>
-      <c r="DP3" s="26"/>
-      <c r="DQ3" s="26"/>
-      <c r="DR3" s="26"/>
-      <c r="DS3" s="26"/>
-      <c r="DT3" s="26"/>
-      <c r="DU3" s="26"/>
-      <c r="DV3" s="26"/>
-      <c r="DW3" s="26"/>
-      <c r="DX3" s="26"/>
-      <c r="DY3" s="26"/>
-      <c r="DZ3" s="26"/>
-      <c r="EA3" s="26"/>
-      <c r="EB3" s="26"/>
-      <c r="EC3" s="26"/>
-      <c r="ED3" s="26"/>
-      <c r="EE3" s="26"/>
-      <c r="EF3" s="26"/>
-      <c r="EG3" s="26"/>
-      <c r="EH3" s="26"/>
-      <c r="EI3" s="26"/>
-      <c r="EJ3" s="26"/>
-      <c r="EK3" s="26"/>
-      <c r="EL3" s="26"/>
-      <c r="EM3" s="26"/>
-      <c r="EN3" s="26"/>
-      <c r="EO3" s="26"/>
-      <c r="EP3" s="26"/>
-      <c r="EQ3" s="26"/>
-      <c r="ER3" s="26"/>
-      <c r="ES3" s="26"/>
-      <c r="ET3" s="26"/>
-      <c r="EU3" s="26"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="44"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="44"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="46"/>
+      <c r="AE3" s="46"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="48"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6">
+        <v>5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>6</v>
+      </c>
+      <c r="G4" s="6">
+        <v>7</v>
+      </c>
+      <c r="H4" s="6">
+        <v>8</v>
+      </c>
+      <c r="I4" s="6">
+        <v>9</v>
+      </c>
+      <c r="J4" s="6">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6">
+        <v>11</v>
+      </c>
+      <c r="L4" s="6">
+        <v>12</v>
+      </c>
+      <c r="M4" s="6">
+        <v>13</v>
+      </c>
+      <c r="N4" s="6">
+        <v>14</v>
+      </c>
+      <c r="O4" s="6">
+        <v>15</v>
+      </c>
+      <c r="P4" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>17</v>
+      </c>
+      <c r="R4" s="6">
+        <v>18</v>
+      </c>
+      <c r="S4" s="6">
+        <v>19</v>
+      </c>
+      <c r="T4" s="6">
+        <v>20</v>
+      </c>
+      <c r="U4" s="6">
+        <v>21</v>
+      </c>
+      <c r="V4" s="6">
+        <v>22</v>
+      </c>
+      <c r="W4" s="6">
+        <v>23</v>
+      </c>
+      <c r="X4" s="6">
+        <v>24</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>25</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>26</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>28</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>29</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>33</v>
+      </c>
+      <c r="AH4" s="6">
+        <v>34</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>35</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>36</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>37</v>
+      </c>
+      <c r="AL4" s="6">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="Q1:T1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:P1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:T1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{4A28C411-2798-4FC9-9CE3-60242289712B}"/>

--- a/Mẫu thông tin nhân viên.xlsx
+++ b/Mẫu thông tin nhân viên.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nghia\Desktop\temp\blockchainHC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E82ED23-6809-45C1-B2AA-62008BDB986D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58771C51-3BE0-4DCE-AF8E-A9275E0714D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0B8F0A66-3EF3-4759-B4C1-B9F12DEC6208}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
   <si>
     <t>STT</t>
   </si>
@@ -927,9 +927,6 @@
     <t>K Bank</t>
   </si>
   <si>
-    <t>Ngô Thanh Tiến</t>
-  </si>
-  <si>
     <t>22/07/2024</t>
   </si>
   <si>
@@ -951,9 +948,6 @@
     <t>THPT</t>
   </si>
   <si>
-    <t>079099014845</t>
-  </si>
-  <si>
     <t>20/12/2021</t>
   </si>
   <si>
@@ -982,6 +976,18 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn C</t>
+  </si>
+  <si>
+    <t>Ngô Thanh Tiến1</t>
+  </si>
+  <si>
+    <t>07909901413845</t>
+  </si>
+  <si>
+    <t>0790990143845</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1500,49 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1517,48 +1565,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1923,61 +1929,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="66" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66" t="s">
+      <c r="D1" s="58"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="53" t="s">
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="69"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="71" t="s">
+      <c r="M1" s="64"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="73" t="s">
+      <c r="P1" s="67"/>
+      <c r="Q1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="53" t="s">
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="54"/>
-      <c r="W1" s="54"/>
-      <c r="X1" s="55" t="s">
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="57" t="s">
+      <c r="Y1" s="70"/>
+      <c r="Z1" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="58" t="s">
+      <c r="AA1" s="70"/>
+      <c r="AB1" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="AC1" s="59"/>
-      <c r="AD1" s="60" t="s">
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="AE1" s="59"/>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="73"/>
       <c r="AH1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1996,7 +2002,7 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:42" ht="82.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="62"/>
+      <c r="A2" s="56"/>
       <c r="B2" s="7" t="s">
         <v>16</v>
       </c>
@@ -2103,78 +2109,78 @@
       <c r="AO2" s="4"/>
       <c r="AP2" s="4"/>
     </row>
-    <row r="3" spans="1:42" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" s="5" customFormat="1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="D3" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="E3" s="30" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="31" t="s">
         <v>48</v>
       </c>
       <c r="G3" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="I3" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="J3" s="34" t="s">
         <v>58</v>
-      </c>
-      <c r="J3" s="34" t="s">
-        <v>59</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>49</v>
       </c>
       <c r="L3" s="35" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M3" s="36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N3" s="25" t="s">
         <v>50</v>
       </c>
       <c r="O3" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="P3" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q3" s="26" t="s">
+      <c r="S3" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="T3" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="S3" s="40" t="s">
+      <c r="U3" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="40" t="s">
+      <c r="V3" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="U3" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="V3" s="27" t="s">
-        <v>68</v>
       </c>
       <c r="W3" s="24" t="s">
         <v>51</v>
       </c>
       <c r="X3" s="42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y3" s="43"/>
       <c r="Z3" s="44"/>
@@ -2193,135 +2199,69 @@
       <c r="AM3" s="39"/>
       <c r="AN3" s="39"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" ht="33" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
-        <v>3</v>
-      </c>
-      <c r="D4" s="6">
-        <v>4</v>
-      </c>
-      <c r="E4" s="6">
-        <v>5</v>
-      </c>
-      <c r="F4" s="6">
-        <v>6</v>
-      </c>
-      <c r="G4" s="6">
-        <v>7</v>
-      </c>
-      <c r="H4" s="6">
-        <v>8</v>
-      </c>
-      <c r="I4" s="6">
-        <v>9</v>
-      </c>
-      <c r="J4" s="6">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6">
-        <v>11</v>
-      </c>
-      <c r="L4" s="6">
-        <v>12</v>
-      </c>
-      <c r="M4" s="6">
-        <v>13</v>
-      </c>
-      <c r="N4" s="6">
-        <v>14</v>
-      </c>
-      <c r="O4" s="6">
-        <v>15</v>
-      </c>
-      <c r="P4" s="6">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>17</v>
-      </c>
-      <c r="R4" s="6">
-        <v>18</v>
-      </c>
-      <c r="S4" s="6">
-        <v>19</v>
-      </c>
-      <c r="T4" s="6">
-        <v>20</v>
-      </c>
-      <c r="U4" s="6">
-        <v>21</v>
-      </c>
-      <c r="V4" s="6">
-        <v>22</v>
-      </c>
-      <c r="W4" s="6">
-        <v>23</v>
-      </c>
-      <c r="X4" s="6">
-        <v>24</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>25</v>
-      </c>
-      <c r="Z4" s="6">
-        <v>26</v>
-      </c>
-      <c r="AA4" s="6">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>28</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>29</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>30</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>31</v>
-      </c>
-      <c r="AF4" s="6">
-        <v>32</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>33</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>34</v>
-      </c>
-      <c r="AI4" s="6">
-        <v>35</v>
-      </c>
-      <c r="AJ4" s="6">
-        <v>36</v>
-      </c>
-      <c r="AK4" s="6">
-        <v>37</v>
-      </c>
-      <c r="AL4" s="6">
-        <v>38</v>
+      <c r="B4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:P1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AG1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R3" r:id="rId1" xr:uid="{4A28C411-2798-4FC9-9CE3-60242289712B}"/>
